--- a/data/trans_orig/P6603-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6603-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a respirar vapores, humos, polvo, o sustancias peligrosas.../Manejar o tocas sustancias o productos peligrosos/Radiaciones como rayos X, soldadura, rayos láseren su trabajo en 2007</t>
+          <t>Población según la exposición a respirar vapores, humos, polvo, o sustancias peligrosas.../Manejar o tocas sustancias o productos peligrosos/Radiaciones como rayos X, soldadura, rayos láseren su trabajo en 2007 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>193405</t>
+          <t>191036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>230119</t>
+          <t>230706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106425</t>
+          <t>107893</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127688</t>
+          <t>129322</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>308340</t>
+          <t>307629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>354493</t>
+          <t>353615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,99%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65913</t>
+          <t>66795</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98883</t>
+          <t>100249</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14728</t>
+          <t>14076</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33269</t>
+          <t>32175</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85084</t>
+          <t>85248</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121973</t>
+          <t>122903</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47484</t>
+          <t>47199</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78359</t>
+          <t>77154</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16888</t>
+          <t>17672</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55567</t>
+          <t>54272</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87846</t>
+          <t>85948</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32777</t>
+          <t>32471</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15709</t>
+          <t>16055</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35378</t>
+          <t>35997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>719715</t>
+          <t>718566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>785599</t>
+          <t>783665</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>471325</t>
+          <t>472872</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>507002</t>
+          <t>508053</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1203339</t>
+          <t>1205711</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1277636</t>
+          <t>1280422</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>168577</t>
+          <t>167946</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>219034</t>
+          <t>219493</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43345</t>
+          <t>44225</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72380</t>
+          <t>72550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>224506</t>
+          <t>224832</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>285223</t>
+          <t>284022</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>112367</t>
+          <t>111685</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>157201</t>
+          <t>156316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16443</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36900</t>
+          <t>37025</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136036</t>
+          <t>134733</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185253</t>
+          <t>184367</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33156</t>
+          <t>31441</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59892</t>
+          <t>59579</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15380</t>
+          <t>15278</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39585</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68826</t>
+          <t>68261</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>319597</t>
+          <t>318236</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>351680</t>
+          <t>351486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>246836</t>
+          <t>246166</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>267459</t>
+          <t>268569</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>572042</t>
+          <t>571615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>610864</t>
+          <t>613030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,34%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30910</t>
+          <t>31177</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57616</t>
+          <t>58146</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11162</t>
+          <t>11843</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28190</t>
+          <t>27914</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>47663</t>
+          <t>46560</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>78487</t>
+          <t>80019</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>24896</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18433</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15193</t>
+          <t>15635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36534</t>
+          <t>35408</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21408</t>
+          <t>20805</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10238</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25994</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1259391</t>
+          <t>1259209</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1341737</t>
+          <t>1345563</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>840703</t>
+          <t>845076</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>889758</t>
+          <t>890475</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2115606</t>
+          <t>2111577</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2211721</t>
+          <t>2212091</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,57%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>288570</t>
+          <t>282871</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>353136</t>
+          <t>350272</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80854</t>
+          <t>80696</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>119561</t>
+          <t>118340</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>376381</t>
+          <t>379699</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>458903</t>
+          <t>460043</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>181791</t>
+          <t>182402</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>233660</t>
+          <t>236134</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33216</t>
+          <t>32025</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59395</t>
+          <t>59508</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>225083</t>
+          <t>222327</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>286413</t>
+          <t>285307</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61776</t>
+          <t>61985</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99006</t>
+          <t>97923</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23452</t>
+          <t>23039</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72561</t>
+          <t>73576</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>111363</t>
+          <t>112267</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a respirar vapores, humos, polvo, o sustancias peligrosas.../Manejar o tocas sustancias o productos peligrosos/Radiaciones como rayos X, soldadura, rayos láseren su trabajo en 2012</t>
+          <t>Población según la exposición a respirar vapores, humos, polvo, o sustancias peligrosas.../Manejar o tocas sustancias o productos peligrosos/Radiaciones como rayos X, soldadura, rayos láseren su trabajo en 2012 (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65701</t>
+          <t>65764</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92610</t>
+          <t>92935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89954</t>
+          <t>89482</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110943</t>
+          <t>111351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160859</t>
+          <t>160779</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>197320</t>
+          <t>198990</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,63%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34934</t>
+          <t>34721</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57889</t>
+          <t>59706</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16248</t>
+          <t>16584</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34575</t>
+          <t>34580</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56336</t>
+          <t>54756</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85660</t>
+          <t>85511</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28429</t>
+          <t>27886</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51083</t>
+          <t>50039</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12813</t>
+          <t>13214</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33127</t>
+          <t>32623</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58449</t>
+          <t>57489</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13535</t>
+          <t>13179</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32301</t>
+          <t>31659</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18044</t>
+          <t>18014</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40513</t>
+          <t>40613</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>461102</t>
+          <t>456007</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>520862</t>
+          <t>518980</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>414648</t>
+          <t>416733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>457232</t>
+          <t>457599</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>886237</t>
+          <t>890060</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>962758</t>
+          <t>968413</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,27%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>210069</t>
+          <t>210162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>262492</t>
+          <t>265070</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65169</t>
+          <t>63544</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98562</t>
+          <t>97089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>289011</t>
+          <t>286899</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>351937</t>
+          <t>352411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93843</t>
+          <t>92170</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134074</t>
+          <t>135712</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24602</t>
+          <t>24284</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48767</t>
+          <t>47594</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125432</t>
+          <t>124739</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>172126</t>
+          <t>169561</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56593</t>
+          <t>55564</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90226</t>
+          <t>89206</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>12540</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30066</t>
+          <t>29726</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73687</t>
+          <t>73293</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110753</t>
+          <t>110573</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>228143</t>
+          <t>229798</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>261562</t>
+          <t>260594</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>185754</t>
+          <t>183554</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>209675</t>
+          <t>208389</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>420909</t>
+          <t>423820</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>463592</t>
+          <t>464989</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32320</t>
+          <t>33181</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59423</t>
+          <t>59880</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15762</t>
+          <t>15554</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35544</t>
+          <t>37191</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>52811</t>
+          <t>53657</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>86913</t>
+          <t>87082</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>10095</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28693</t>
+          <t>28832</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15593</t>
+          <t>15957</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17119</t>
+          <t>17406</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39550</t>
+          <t>37978</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15366</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>11183</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21368</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>779147</t>
+          <t>775682</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>853389</t>
+          <t>851587</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>710620</t>
+          <t>708778</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>763300</t>
+          <t>760894</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1504232</t>
+          <t>1506138</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1600433</t>
+          <t>1597642</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,79%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293639</t>
+          <t>293129</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>361539</t>
+          <t>360698</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109955</t>
+          <t>110453</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>151649</t>
+          <t>156615</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>422471</t>
+          <t>421316</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>498958</t>
+          <t>498681</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>144065</t>
+          <t>144418</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>195303</t>
+          <t>193710</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37750</t>
+          <t>35998</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67216</t>
+          <t>63809</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>188510</t>
+          <t>188707</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>249237</t>
+          <t>250074</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80819</t>
+          <t>79727</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122713</t>
+          <t>122406</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20229</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42121</t>
+          <t>43246</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>107282</t>
+          <t>108894</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>152962</t>
+          <t>153020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a respirar vapores, humos, polvo, o sustancias peligrosas.../Manejar o tocas sustancias o productos peligrosos/Radiaciones como rayos X, soldadura, rayos láseren su trabajo en 2016</t>
+          <t>Población según la exposición a respirar vapores, humos, polvo, o sustancias peligrosas.../Manejar o tocas sustancias o productos peligrosos/Radiaciones como rayos X, soldadura, rayos láseren su trabajo en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38029</t>
+          <t>37638</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60252</t>
+          <t>61869</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40664</t>
+          <t>40304</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56522</t>
+          <t>56541</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84046</t>
+          <t>83919</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112749</t>
+          <t>112556</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,08%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37405</t>
+          <t>36970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60498</t>
+          <t>60654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25261</t>
+          <t>25694</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53761</t>
+          <t>53539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82685</t>
+          <t>80261</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>37,85%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20109</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40236</t>
+          <t>41008</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24316</t>
+          <t>25347</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47366</t>
+          <t>47387</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21806</t>
+          <t>22866</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6976</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22624</t>
+          <t>23372</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>458829</t>
+          <t>462324</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>521021</t>
+          <t>522425</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>446878</t>
+          <t>446904</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>493032</t>
+          <t>493377</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>926119</t>
+          <t>923900</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1003315</t>
+          <t>1001970</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,73%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>226007</t>
+          <t>225766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>280502</t>
+          <t>279961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92532</t>
+          <t>95593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132257</t>
+          <t>132131</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>332487</t>
+          <t>332250</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>400819</t>
+          <t>399756</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117777</t>
+          <t>117794</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160893</t>
+          <t>164681</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38689</t>
+          <t>38079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65788</t>
+          <t>66986</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162685</t>
+          <t>163207</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>215910</t>
+          <t>216403</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28273</t>
+          <t>27830</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52630</t>
+          <t>53306</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26734</t>
+          <t>26637</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42772</t>
+          <t>41352</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72932</t>
+          <t>72198</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241631</t>
+          <t>241065</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>274334</t>
+          <t>274485</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>248539</t>
+          <t>246760</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>274104</t>
+          <t>272192</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>496786</t>
+          <t>498142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>540167</t>
+          <t>540926</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48209</t>
+          <t>46710</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79018</t>
+          <t>77985</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23165</t>
+          <t>23109</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44064</t>
+          <t>45200</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>77347</t>
+          <t>75288</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>115487</t>
+          <t>113637</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32604</t>
+          <t>32705</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>12606</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18987</t>
+          <t>19470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40392</t>
+          <t>40898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13859</t>
+          <t>14243</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>23290</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>759250</t>
+          <t>764370</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>836595</t>
+          <t>838533</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>752211</t>
+          <t>753773</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>808165</t>
+          <t>810209</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1533069</t>
+          <t>1529828</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1632979</t>
+          <t>1632045</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,88%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>334486</t>
+          <t>331211</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>401823</t>
+          <t>397340</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>140011</t>
+          <t>137965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>187125</t>
+          <t>185118</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>485119</t>
+          <t>482001</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>564412</t>
+          <t>565985</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>162534</t>
+          <t>162791</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>216451</t>
+          <t>216218</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49510</t>
+          <t>48091</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78152</t>
+          <t>79061</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>220083</t>
+          <t>223346</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>284163</t>
+          <t>285016</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43308</t>
+          <t>43658</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74439</t>
+          <t>74725</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35258</t>
+          <t>36217</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63466</t>
+          <t>63856</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100852</t>
+          <t>101046</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a respirar vapores, humos, polvo, o sustancias peligrosas.../Manejar o tocas sustancias o productos peligrosos/Radiaciones como rayos X, soldadura, rayos láseren su trabajo en 2023</t>
+          <t>Población según la exposición a respirar vapores, humos, polvo, o sustancias peligrosas.../Manejar o tocas sustancias o productos peligrosos/Radiaciones como rayos X, soldadura, rayos láseren su trabajo en 2023 (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24554</t>
+          <t>24921</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42167</t>
+          <t>41584</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17695</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27628</t>
+          <t>27574</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45513</t>
+          <t>46564</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65455</t>
+          <t>64712</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>15076</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31092</t>
+          <t>30894</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19014</t>
+          <t>18980</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27627</t>
+          <t>27578</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46097</t>
+          <t>45242</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,28%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10910</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>524</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12782</t>
+          <t>12921</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>10815</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12448</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>395564</t>
+          <t>392037</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>689936</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>281916</t>
+          <t>282065</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>330328</t>
+          <t>333606</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>715202</t>
+          <t>716090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1003960</t>
+          <t>1041768</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>83,78%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82470</t>
+          <t>76924</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>283038</t>
+          <t>287750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76497</t>
+          <t>77437</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116006</t>
+          <t>118519</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164462</t>
+          <t>147420</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>370719</t>
+          <t>371898</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,91%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28693</t>
+          <t>25988</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105162</t>
+          <t>105489</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>14696</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31043</t>
+          <t>31676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46963</t>
+          <t>44745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>121444</t>
+          <t>122055</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33266</t>
+          <t>33731</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24898</t>
+          <t>24776</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18563</t>
+          <t>17248</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>52262</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>190440</t>
+          <t>192532</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>215686</t>
+          <t>215795</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161999</t>
+          <t>161491</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179832</t>
+          <t>180127</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>360695</t>
+          <t>362032</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>390356</t>
+          <t>390989</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17841</t>
+          <t>18143</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36974</t>
+          <t>36640</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>10537</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24733</t>
+          <t>24382</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>32874</t>
+          <t>31282</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>55674</t>
+          <t>55831</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17003</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>17944</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25400</t>
+          <t>25276</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>656908</t>
+          <t>658225</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>933190</t>
+          <t>926170</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>477023</t>
+          <t>472737</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>529055</t>
+          <t>527102</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1164436</t>
+          <t>1161837</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1447701</t>
+          <t>1460146</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,61%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>122721</t>
+          <t>128718</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>319715</t>
+          <t>315511</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>105481</t>
+          <t>106739</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>148772</t>
+          <t>150833</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>239670</t>
+          <t>236802</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>442128</t>
+          <t>444458</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36642</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>109941</t>
+          <t>107472</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17795</t>
+          <t>17928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34625</t>
+          <t>34192</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>66213</t>
+          <t>65218</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>128452</t>
+          <t>131534</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>13237</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43379</t>
+          <t>44384</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17187</t>
+          <t>17766</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36843</t>
+          <t>36260</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33079</t>
+          <t>32977</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72812</t>
+          <t>73576</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6603-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6603-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>191036</t>
+          <t>194420</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>230706</t>
+          <t>233017</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107893</t>
+          <t>108301</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129322</t>
+          <t>129792</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>307629</t>
+          <t>307351</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>353615</t>
+          <t>352779</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,83%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66795</t>
+          <t>65224</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100249</t>
+          <t>97570</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32175</t>
+          <t>32036</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85248</t>
+          <t>84054</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122903</t>
+          <t>122236</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47199</t>
+          <t>47710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77154</t>
+          <t>75538</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17672</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54272</t>
+          <t>55729</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85948</t>
+          <t>86038</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>13778</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32471</t>
+          <t>31942</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7683</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16055</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35997</t>
+          <t>36164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>718566</t>
+          <t>721687</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>783665</t>
+          <t>785386</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>472872</t>
+          <t>472363</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>508053</t>
+          <t>507829</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1205711</t>
+          <t>1204141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1280422</t>
+          <t>1276238</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,83%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167946</t>
+          <t>168155</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>219493</t>
+          <t>222572</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44225</t>
+          <t>43863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72550</t>
+          <t>72337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>224832</t>
+          <t>225653</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>284022</t>
+          <t>282566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>111685</t>
+          <t>113769</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>156316</t>
+          <t>156878</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16958</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37025</t>
+          <t>36804</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134733</t>
+          <t>136210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>184367</t>
+          <t>183614</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31441</t>
+          <t>32429</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59579</t>
+          <t>60306</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15278</t>
+          <t>15488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>40103</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68261</t>
+          <t>68768</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>318236</t>
+          <t>319277</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>351486</t>
+          <t>350137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>246166</t>
+          <t>244663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>268569</t>
+          <t>267827</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>571615</t>
+          <t>573687</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>613030</t>
+          <t>612731</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31177</t>
+          <t>30167</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58146</t>
+          <t>56303</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11843</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27914</t>
+          <t>29041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>46560</t>
+          <t>46038</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>80019</t>
+          <t>79149</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24896</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17654</t>
+          <t>18425</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15635</t>
+          <t>15902</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35408</t>
+          <t>35829</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20805</t>
+          <t>22104</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25813</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1259209</t>
+          <t>1255656</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1345563</t>
+          <t>1337941</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>845076</t>
+          <t>842658</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>890475</t>
+          <t>889304</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2111577</t>
+          <t>2118440</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2212091</t>
+          <t>2214302</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,64%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282871</t>
+          <t>288368</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>350272</t>
+          <t>354268</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80696</t>
+          <t>81518</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>118340</t>
+          <t>119157</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>379699</t>
+          <t>381825</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>460043</t>
+          <t>458727</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>182402</t>
+          <t>182482</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>236134</t>
+          <t>238683</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32025</t>
+          <t>32456</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59508</t>
+          <t>59005</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>222327</t>
+          <t>222824</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>285307</t>
+          <t>286625</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61985</t>
+          <t>61979</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97923</t>
+          <t>97534</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23039</t>
+          <t>22916</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73576</t>
+          <t>73378</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112267</t>
+          <t>112961</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65764</t>
+          <t>65751</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92935</t>
+          <t>92128</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89482</t>
+          <t>88719</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111351</t>
+          <t>110581</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160779</t>
+          <t>162556</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>198990</t>
+          <t>198089</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34721</t>
+          <t>34206</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59706</t>
+          <t>58491</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16584</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34580</t>
+          <t>36578</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54756</t>
+          <t>54261</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85511</t>
+          <t>84763</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27886</t>
+          <t>26795</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50039</t>
+          <t>49947</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13214</t>
+          <t>14034</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32623</t>
+          <t>33691</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57489</t>
+          <t>58472</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13179</t>
+          <t>13662</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31659</t>
+          <t>32307</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>13067</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18014</t>
+          <t>19051</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40613</t>
+          <t>40135</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>456007</t>
+          <t>459358</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518980</t>
+          <t>520173</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>416733</t>
+          <t>416034</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>457599</t>
+          <t>456539</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>890060</t>
+          <t>888573</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>968413</t>
+          <t>966937</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>210162</t>
+          <t>210537</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>265070</t>
+          <t>266975</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63544</t>
+          <t>63988</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97089</t>
+          <t>100055</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>286899</t>
+          <t>285572</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>352411</t>
+          <t>354551</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92170</t>
+          <t>91032</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135712</t>
+          <t>135092</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24284</t>
+          <t>23567</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47594</t>
+          <t>48554</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124739</t>
+          <t>121906</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>169561</t>
+          <t>170274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55564</t>
+          <t>56188</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89206</t>
+          <t>93171</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12540</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29726</t>
+          <t>29690</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73293</t>
+          <t>73143</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110573</t>
+          <t>113281</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>229798</t>
+          <t>229910</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>260594</t>
+          <t>262489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>183554</t>
+          <t>184357</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208389</t>
+          <t>208276</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>423820</t>
+          <t>423118</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>464989</t>
+          <t>464878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,5%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33181</t>
+          <t>32598</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59880</t>
+          <t>59320</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15554</t>
+          <t>15645</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37191</t>
+          <t>36997</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>53657</t>
+          <t>52700</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>87082</t>
+          <t>86727</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28832</t>
+          <t>30334</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15957</t>
+          <t>16536</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17406</t>
+          <t>16583</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37978</t>
+          <t>39187</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13862</t>
+          <t>15096</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11183</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20186</t>
+          <t>20012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>775682</t>
+          <t>777839</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>851587</t>
+          <t>853136</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>708778</t>
+          <t>709697</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>760894</t>
+          <t>761488</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1506138</t>
+          <t>1504059</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1597642</t>
+          <t>1599331</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,87%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293129</t>
+          <t>294938</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>360698</t>
+          <t>361096</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>110453</t>
+          <t>108717</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156615</t>
+          <t>151800</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>421316</t>
+          <t>421425</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>498681</t>
+          <t>497610</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>144418</t>
+          <t>144075</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>193710</t>
+          <t>196326</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35998</t>
+          <t>37218</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>67245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>188707</t>
+          <t>189264</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>250074</t>
+          <t>248374</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79727</t>
+          <t>83064</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122406</t>
+          <t>122006</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>21106</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43246</t>
+          <t>43772</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108894</t>
+          <t>109214</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>153020</t>
+          <t>155249</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37638</t>
+          <t>37313</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61869</t>
+          <t>60582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40304</t>
+          <t>41102</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56541</t>
+          <t>56691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83919</t>
+          <t>83664</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112556</t>
+          <t>112492</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>53,05%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36970</t>
+          <t>37699</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60654</t>
+          <t>59418</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11635</t>
+          <t>11250</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25694</t>
+          <t>25670</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53539</t>
+          <t>53055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80261</t>
+          <t>80734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,07%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20637</t>
+          <t>19937</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41008</t>
+          <t>40800</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25347</t>
+          <t>23554</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47387</t>
+          <t>47133</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7272</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22866</t>
+          <t>22091</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23372</t>
+          <t>23790</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>462324</t>
+          <t>462992</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>522425</t>
+          <t>524197</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>446904</t>
+          <t>448550</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>493377</t>
+          <t>494196</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>923900</t>
+          <t>924549</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1001970</t>
+          <t>1002126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>225766</t>
+          <t>223088</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>279961</t>
+          <t>280980</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95593</t>
+          <t>95113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132131</t>
+          <t>135536</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>332250</t>
+          <t>332158</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>399756</t>
+          <t>401965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117794</t>
+          <t>113087</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>164681</t>
+          <t>159115</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38079</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66986</t>
+          <t>66064</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163207</t>
+          <t>164730</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>216403</t>
+          <t>215600</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27830</t>
+          <t>27594</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53306</t>
+          <t>52497</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26637</t>
+          <t>26263</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>41352</t>
+          <t>41917</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72198</t>
+          <t>72513</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241065</t>
+          <t>242020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>274485</t>
+          <t>276025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>246760</t>
+          <t>247087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>272192</t>
+          <t>271733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>498142</t>
+          <t>498359</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>540926</t>
+          <t>540649</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46710</t>
+          <t>49484</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>77985</t>
+          <t>77817</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23109</t>
+          <t>22588</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45200</t>
+          <t>44292</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>75288</t>
+          <t>75591</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>113637</t>
+          <t>112961</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>13709</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32705</t>
+          <t>33151</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12606</t>
+          <t>13527</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19470</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40898</t>
+          <t>40149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>11959</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>14273</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23290</t>
+          <t>21874</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>764370</t>
+          <t>762313</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>838533</t>
+          <t>839613</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>753773</t>
+          <t>755425</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>810209</t>
+          <t>809890</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1529828</t>
+          <t>1534918</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1632045</t>
+          <t>1631970</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,87%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>331211</t>
+          <t>327497</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>397340</t>
+          <t>398004</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>137965</t>
+          <t>141056</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>185118</t>
+          <t>187366</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>482001</t>
+          <t>480760</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>565985</t>
+          <t>564366</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>162791</t>
+          <t>163694</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>216218</t>
+          <t>214260</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,82 +7695,82 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>11,62%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>15,21%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>62756</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>48436</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>80446</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>251137</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>221972</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>281838</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>10,29%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
           <t>11,55%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>15,35%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>62756</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>48091</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>79061</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>251137</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>223346</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>285016</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43658</t>
+          <t>44378</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74725</t>
+          <t>75514</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15800</t>
+          <t>15717</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36217</t>
+          <t>36183</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63856</t>
+          <t>63402</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>101046</t>
+          <t>100030</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33413</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24921</t>
+          <t>29127</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41584</t>
+          <t>51168</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22604</t>
+          <t>26530</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27574</t>
+          <t>31918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>56017</t>
+          <t>65512</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46564</t>
+          <t>52249</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>77419</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22488</t>
+          <t>27091</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15076</t>
+          <t>17476</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30894</t>
+          <t>37553</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14069</t>
+          <t>17092</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9152</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18980</t>
+          <t>23761</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>36557</t>
+          <t>44183</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27578</t>
+          <t>33546</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45242</t>
+          <t>55501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>41,38%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>16613</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>29576</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>18490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>34338</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10815</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>677</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -8633,57 +8633,57 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>5944</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2249</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>12549</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>1,68%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>5608</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>2346</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>11965</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>528857</t>
+          <t>313336</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>392037</t>
+          <t>287023</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>689936</t>
+          <t>341481</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>302457</t>
+          <t>299785</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>282065</t>
+          <t>282147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>333606</t>
+          <t>317965</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>831314</t>
+          <t>613121</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>716090</t>
+          <t>581387</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1041768</t>
+          <t>647205</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>60,36%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>188560</t>
+          <t>210096</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76924</t>
+          <t>183463</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>287750</t>
+          <t>236169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>98904</t>
+          <t>110134</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77437</t>
+          <t>94950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118519</t>
+          <t>127172</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>287464</t>
+          <t>320229</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>147420</t>
+          <t>289144</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>371898</t>
+          <t>354424</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67043</t>
+          <t>74359</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25988</t>
+          <t>56960</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105489</t>
+          <t>93455</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22183</t>
+          <t>24953</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>17198</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31676</t>
+          <t>34612</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>89227</t>
+          <t>99313</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44745</t>
+          <t>77948</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>122055</t>
+          <t>122399</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19110</t>
+          <t>21382</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>12418</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33731</t>
+          <t>32907</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16315</t>
+          <t>18122</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>11794</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24776</t>
+          <t>27181</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>35425</t>
+          <t>39504</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>28788</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52262</t>
+          <t>51896</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>803570</t>
+          <t>619173</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>803570</t>
+          <t>619173</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>803570</t>
+          <t>619173</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>439859</t>
+          <t>452993</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>439859</t>
+          <t>452993</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>439859</t>
+          <t>452993</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1243429</t>
+          <t>1072166</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1243429</t>
+          <t>1072166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1243429</t>
+          <t>1072166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>205665</t>
+          <t>227161</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>192532</t>
+          <t>211478</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>215795</t>
+          <t>237451</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>172053</t>
+          <t>189653</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161491</t>
+          <t>179729</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180127</t>
+          <t>198435</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>377718</t>
+          <t>416814</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>362032</t>
+          <t>398483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>390989</t>
+          <t>433107</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,82%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26258</t>
+          <t>29954</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18143</t>
+          <t>21438</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36640</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16596</t>
+          <t>17038</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10537</t>
+          <t>11136</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24382</t>
+          <t>25115</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>46992</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>31282</t>
+          <t>35079</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>55831</t>
+          <t>59684</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12717</t>
+          <t>14687</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14615</t>
+          <t>15513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -9736,12 +9736,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17481</t>
+          <t>23160</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17944</t>
+          <t>20440</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>16292</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25276</t>
+          <t>29964</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>767934</t>
+          <t>579479</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>658225</t>
+          <t>546309</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>926170</t>
+          <t>616688</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>497114</t>
+          <t>515968</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>472737</t>
+          <t>494706</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>527102</t>
+          <t>537979</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1265049</t>
+          <t>1095447</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1161837</t>
+          <t>1056053</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1460146</t>
+          <t>1138679</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>67,22%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>237305</t>
+          <t>267141</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>128718</t>
+          <t>236869</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>315511</t>
+          <t>298034</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>129569</t>
+          <t>144263</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>106739</t>
+          <t>126743</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>150833</t>
+          <t>164275</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>366874</t>
+          <t>411404</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>236802</t>
+          <t>375213</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>444458</t>
+          <t>448510</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>77418</t>
+          <t>97031</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>75828</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>107472</t>
+          <t>123848</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25391</t>
+          <t>28291</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>20253</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34192</t>
+          <t>38592</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>102809</t>
+          <t>125322</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>65218</t>
+          <t>100872</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>131534</t>
+          <t>152448</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>31610</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13237</t>
+          <t>21468</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44384</t>
+          <t>48081</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>25974</t>
+          <t>30129</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17766</t>
+          <t>21385</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36260</t>
+          <t>42303</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>54358</t>
+          <t>61739</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32977</t>
+          <t>47552</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73576</t>
+          <t>80543</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1111042</t>
+          <t>975260</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1111042</t>
+          <t>975260</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1111042</t>
+          <t>975260</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>678048</t>
+          <t>718652</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>678048</t>
+          <t>718652</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>678048</t>
+          <t>718652</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1789090</t>
+          <t>1693912</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1789090</t>
+          <t>1693912</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1789090</t>
+          <t>1693912</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
